--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>44985</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45894</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45570</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45743</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46191</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45337</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45418</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45798</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45309</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44924</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45712</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45402</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44797</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44942</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45183</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45393</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44949</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>45336</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45418</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44930</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45096</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44943</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46044</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45622</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44841</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45576</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45425</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45691</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45446</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44968</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45439</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44574</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45336</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44968</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45233</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>44939</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45233</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45439</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45981</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44462</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44939</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44964</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44935</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>46010</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45720</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45854</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45567</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44857</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45939</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45439</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45701</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44550</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45335</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45183</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45166</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44881</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45980</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>44040</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45264</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45692</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45628</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45673</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45233</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>46114</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>46057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45159</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46062</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>46055</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>46239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44833</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44647</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44516</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45265</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45205</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45617</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45673</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45040</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44468</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45378</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46129</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45183</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44508</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45419</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45366</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45695</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44698</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45477</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45301</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45840</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45665</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45467</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>46008</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44609</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>46084</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>46190</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45477</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45198</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44628</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>44771</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>44678</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44508</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45448</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44725</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45097</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45335</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45338</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44924</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45212</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44821</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44934</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44847</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44968</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45582</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44929</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45302</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45595</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45072</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44839</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46085</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>44530</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45305</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44938</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44504</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45705</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>46188</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>46094</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>44917</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46203</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>45379</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>46121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45403</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45687</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>46052</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45236</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>46125</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>46148</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44511</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46280</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45700</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45363</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45524</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45826</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45830</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45159</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44824</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45688</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44459</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44839</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44674</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>44725</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44713</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44725</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44496</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44487</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44538</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44713</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44841</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44876</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>44515</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44652</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44482</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44647</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>44647</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44483</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44929</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45039</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45301</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44839</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45086</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44881</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44968</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45322</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45597</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>44467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45667</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44496</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>44959</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45327</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45521</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44698</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45653</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45638</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45691</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45197</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>44966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45207</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45461</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45443</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45418</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45475</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>44712</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45337</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45212</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45281</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45260</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45058</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44609</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45301</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45499</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45290</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45301</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45203</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45635</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45730</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45079</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>44760</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44624</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45349</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>45734</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45102</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45737</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45852</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45852</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45183</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45575</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45173</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45733</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45891</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45895</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45246</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45856</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45895</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44896</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45397</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45772</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45349</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45823</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>44936</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44944</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44955</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45541</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44699</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45837</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45070</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45161</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45013</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45278</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45705</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45705</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45647</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45401</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44968</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44881</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45264</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>44882</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45806</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45669</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45670</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44897</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44931</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45928</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45931</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45335</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45680</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45491</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45856</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45706</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45931</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>45672</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>44998</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45314</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45363</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45177</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45743</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45539</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45112</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45197</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44987</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46154</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46154</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>44841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>46154</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45029</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45978</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>44741</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44936</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45695</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44944</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46160</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46161</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45868</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45407</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>44833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45852</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>45561</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>44705</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44682</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45274</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45615</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>46009</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>44855</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45076</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45281</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44929</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>44929</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>45301</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>46000</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44963</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46024</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45601</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45336</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45161</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>46170</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45418</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>46036</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45078</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45213</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45733</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>46048</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>46048</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>46048</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>45593</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45147</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>45376</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>46062</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>46036</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>46071</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>46071</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45705</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>46184</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44955</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>46083</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>45415</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>46040</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>46188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45197</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45179</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>46008</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>46094</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45250</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45072</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45477</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45607</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46195</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>46198</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>45671</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45491</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>44944</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44988</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>46114</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45709</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>46128</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45602</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45576</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45163</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>44944</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45072</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45807</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44938</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45180</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>46203</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45764</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45370</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>45804</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>45575</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>44699</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44959</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45673</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45695</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45695</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>44909</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45071</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44733</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45716</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>44909</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45509</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45056</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>45686</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45394</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45595</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46213</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>46213</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45097</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45284</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46218</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45585</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46260</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>44818</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>44818</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45418</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45652</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45728</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46076</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46226</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46226</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45440</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>45415</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>46268</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>46268</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45782</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46071</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>46163</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>46154</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>46188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45441</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45368</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45240</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45103</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45791</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45793</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>46237</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45743</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46071</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46240</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46239</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46282</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45700</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45693</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46008</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46071</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45706</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45709</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45822</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45826</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45632</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45750</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45852</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45514</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45830</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45744</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45743</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45571</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45758</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>45763</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45852</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45779</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45698</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45756</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45764</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45774</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45406</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45350</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45209</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>44846</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45390</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45237</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45645</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45784</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45876</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>46139</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45726</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>46149</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44985</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45894</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45570</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45743</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46191</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45337</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45418</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>44924</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46246</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45712</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45265</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45743</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45402</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45637</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44509</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44797</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44942</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45183</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45371</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45393</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46010</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45336</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45477</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44943</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44930</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45425</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44841</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45622</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44928</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45512</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45446</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>44574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45439</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44968</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45336</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45233</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45439</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45233</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44968</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44964</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44939</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45567</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44857</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45439</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45183</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44510</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45335</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45183</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45567</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45166</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45980</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>46114</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46057</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45233</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45692</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45673</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46062</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>46239</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46286</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45673</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>46129</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>44468</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45524</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45531</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45040</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45617</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>46185</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44647</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45183</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45378</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45205</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45265</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45695</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45366</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44839</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44698</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46008</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>46084</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45840</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45301</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45665</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44609</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46209</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45477</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>46190</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45477</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>44628</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44771</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>44678</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45379</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45335</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44847</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45097</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45467</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45687</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44917</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45403</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44968</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46048</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>44508</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46121</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44924</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44839</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45212</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44530</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44934</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45582</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44504</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45826</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>46085</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45305</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44938</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45705</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45338</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45830</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46203</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44821</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45526</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>46052</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45302</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>46125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46148</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44511</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45072</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45448</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44725</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45212</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45236</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45159</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44824</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45688</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46202</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44839</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>44674</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44725</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44725</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44496</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44487</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44538</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44713</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44841</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44515</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>44652</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44482</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44647</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44647</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44483</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44760</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45443</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44841</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>44516</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45207</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45363</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45418</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44896</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44699</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45743</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46024</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45274</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45700</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45793</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45491</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44938</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45337</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45733</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45852</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45852</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45635</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46036</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45693</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45521</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45891</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45895</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45895</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45477</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45647</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>46062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45418</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45349</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>46071</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>46071</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>46071</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45806</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45335</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45928</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46040</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45179</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45856</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45709</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45705</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45705</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45939</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46009</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45939</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>46008</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44699</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44855</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44897</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45112</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44968</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45076</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45281</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45706</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45671</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45056</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45709</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45978</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45000</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44998</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44929</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45602</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45807</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45823</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45804</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45673</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46008</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45772</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45837</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45575</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45669</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>46035</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45868</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45187</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45029</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46057</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45653</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44987</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45161</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44833</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>46009</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45695</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45695</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45822</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45212</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45039</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44467</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45197</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45826</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45418</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45632</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>45705</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45601</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>44936</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45670</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46154</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45086</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45079</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>46154</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>46154</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44968</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45301</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45852</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>44909</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45103</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45190</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45852</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45514</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45322</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45575</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45744</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45571</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45830</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45763</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45852</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45576</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44974</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45284</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45415</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45401</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45336</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44881</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45407</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45173</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45394</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45509</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45733</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45779</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45585</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>46198</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44624</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45764</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46203</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45774</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45667</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44818</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45597</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45197</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45440</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44609</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45652</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46213</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>44698</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45728</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45163</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46213</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45415</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>46218</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>46260</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45180</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46226</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>46226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46268</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45301</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45070</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45730</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45397</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44496</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45541</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>44712</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46237</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>44881</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45290</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>46239</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46008</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>46282</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46286</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46071</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>46071</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46240</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46071</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44682</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44909</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45791</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>46154</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45376</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45264</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>46160</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>46188</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46188</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45281</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46076</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44955</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44955</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44818</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>44931</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44963</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45764</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44944</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>44988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>44944</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45716</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45097</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45461</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44705</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44929</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44944</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45327</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45222</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>44882</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44733</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45183</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44741</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45370</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45475</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45743</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45734</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44839</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45250</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45213</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45301</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45102</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45183</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45680</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45539</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45314</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45260</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44819</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45499</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45491</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45638</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45706</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45615</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45686</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45695</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45349</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45782</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>45240</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45368</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45103</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45441</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45406</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45350</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45209</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>44846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45390</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45237</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45645</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45784</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45876</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46139</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45726</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46149</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44985</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45894</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45570</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45743</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46191</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45337</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45418</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>44924</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46246</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45712</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45265</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45743</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45402</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45637</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44509</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44797</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44942</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45183</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45371</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45393</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46010</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45336</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45477</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44943</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44930</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45425</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44841</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45622</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44928</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45512</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45446</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>44574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45439</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44968</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45336</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45233</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45439</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45233</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44968</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44964</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44939</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45524</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45567</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44857</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45439</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45183</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44510</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45335</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45183</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45567</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45166</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45980</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>46114</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46057</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45233</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45692</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45673</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46062</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>46239</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46286</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45673</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>46129</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>44468</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45524</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45531</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45040</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45617</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>46185</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44647</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45183</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45378</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45205</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45265</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45695</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45366</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44839</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44698</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46008</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>46084</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45840</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45301</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45665</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44609</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46209</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45477</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>46190</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45477</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>44628</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44771</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>44678</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45379</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45335</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44847</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45097</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45467</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45687</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44917</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45403</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44968</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46048</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>44508</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46121</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44924</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44839</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45212</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44530</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44934</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45582</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44504</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45826</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>46085</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45305</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44938</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45705</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45338</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45830</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46203</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44821</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45526</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>46052</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45302</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>46125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46148</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44511</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45072</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45448</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44725</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45212</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45236</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45159</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44824</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45688</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46202</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44839</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>44674</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44725</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44725</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44496</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44487</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44538</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44713</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44841</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44515</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>44652</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44482</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44647</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44647</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44483</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44760</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45443</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44841</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>44516</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45207</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45363</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45418</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44896</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44699</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45743</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46024</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45274</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45700</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45793</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45491</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44938</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45337</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45733</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45852</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45852</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45635</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46036</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45693</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45521</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45891</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45895</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45895</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45477</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45647</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>46062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45418</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45349</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>46071</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>46071</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>46071</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45806</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45335</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45928</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46040</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45179</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45856</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45709</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45705</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45705</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45939</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46009</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45939</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>46008</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44699</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44855</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44897</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45112</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44968</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45076</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45281</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45706</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45671</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45056</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45709</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45978</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45000</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44998</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44929</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45602</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45807</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45823</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45804</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45673</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46008</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45772</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45837</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45575</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45669</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>46035</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45868</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45187</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45029</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46057</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45653</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44987</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45161</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44833</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>46009</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45695</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45695</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45822</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45212</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45039</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44467</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45197</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45826</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45418</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45632</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>45705</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45601</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>44936</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45670</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46154</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45086</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45079</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>46154</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>46154</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44968</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45301</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45852</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>44909</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45103</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45190</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45852</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45514</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45322</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45575</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45744</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45571</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45830</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45763</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45852</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45576</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44974</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45284</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45415</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45401</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45336</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44881</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45407</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45173</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45394</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45509</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45733</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45779</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45585</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>46198</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44624</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45764</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46203</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45774</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45667</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44818</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45597</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45197</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45440</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44609</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45652</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46213</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>44698</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45728</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45163</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46213</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45415</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>46218</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>46260</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45180</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46226</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>46226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46268</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45301</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45070</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45730</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45397</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44496</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45541</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>44712</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46237</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>44881</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45290</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>46239</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46008</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>46282</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46286</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46071</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>46071</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46240</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46071</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44682</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44909</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45791</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>46154</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45376</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45264</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>46160</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>46188</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46188</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45281</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46076</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44955</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44955</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44818</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>44931</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44963</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45764</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44944</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>44988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>44944</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45716</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45097</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45461</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44705</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44929</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44944</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45327</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45222</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>44882</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44733</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45183</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44741</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45370</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45475</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45743</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45734</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44839</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45250</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45213</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45301</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45102</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45183</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45680</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45539</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45314</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45260</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44819</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45499</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45491</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45638</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45706</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45615</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45686</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45695</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45349</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45782</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>45240</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45368</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45103</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45441</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45406</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45350</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45209</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>44846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45390</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45237</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45645</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45784</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45876</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46139</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45726</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46149</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>44985</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45842</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45894</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45570</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45743</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>46191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45418</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>44924</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46246</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45712</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>45265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45402</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44797</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44942</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45183</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45393</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45477</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45336</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45096</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44841</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>44928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45425</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45446</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44968</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45439</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45336</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44968</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44939</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45233</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45439</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45233</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44964</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44935</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45524</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45567</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44857</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45439</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44550</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45166</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45335</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45567</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45264</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45628</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46114</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>46057</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45233</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45673</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46062</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>46239</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44915</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44833</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45366</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44647</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44516</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46129</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45673</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45040</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45378</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45183</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44508</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44496</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45477</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>46008</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45301</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45665</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>46209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45467</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44609</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45477</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44628</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44771</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44678</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45448</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44725</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>44508</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45335</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45212</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45338</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44924</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45467</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44821</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45097</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45700</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46048</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>44934</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44847</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45363</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45582</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45302</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45526</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45830</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45595</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44755</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45072</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44839</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44530</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>46203</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45305</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44504</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>46125</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>46148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45720</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45379</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45403</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45687</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>45159</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45688</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44839</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44674</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44725</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44713</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44725</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44496</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44487</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>44538</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>44713</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>44841</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44876</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44515</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44652</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44647</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>44647</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45039</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45265</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45301</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45086</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45322</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44881</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45441</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45368</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45240</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44968</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45667</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45597</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44699</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45852</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>45222</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>46009</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44959</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45852</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45327</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>44698</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>46024</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45891</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45521</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45653</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45638</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45691</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45793</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45743</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45700</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>46048</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>46048</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>46048</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45207</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45461</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45806</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45928</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45443</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45418</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>46062</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45475</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45337</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45856</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45939</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>46071</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>46071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>46083</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>46040</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45058</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45260</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45301</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45499</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45179</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45000</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>44609</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45706</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>46008</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44516</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45635</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45730</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45079</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44760</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45349</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44624</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45709</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45102</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45822</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45868</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45722</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46128</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45183</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45173</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45632</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>46008</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45807</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45804</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45750</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45397</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45349</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45673</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44955</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45541</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45737</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45575</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45852</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45013</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45278</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45705</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45705</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>45647</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45401</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45514</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45772</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46057</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44881</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45823</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44882</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45669</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45670</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>44897</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45837</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45335</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45680</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45132</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45491</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45706</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45672</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45830</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>45571</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45763</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45852</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44998</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45314</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45363</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45177</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46154</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46154</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46154</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45539</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45852</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>44841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45029</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44741</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44936</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45695</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45779</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45698</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45764</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45774</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45407</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>44833</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45733</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45561</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46184</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>44705</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>44682</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45274</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45615</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44855</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>45076</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45183</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45281</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>44929</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>44929</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45301</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>44963</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45601</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45336</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45161</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45418</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45213</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45733</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46213</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>46213</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46218</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>44988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45376</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45282</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46226</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46226</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46268</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>45705</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44955</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45187</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45415</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45197</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46237</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46239</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46282</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46240</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45072</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45477</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45607</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45791</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45671</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>45491</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44944</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44988</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>46188</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46154</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45709</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46188</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46160</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46292</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46076</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45602</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45576</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45163</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45895</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>46293</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>44944</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45072</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>44938</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45180</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45764</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45370</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>44699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>44959</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45695</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45695</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45071</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46071</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>46071</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46071</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44733</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46195</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45716</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>44909</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45509</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45056</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45394</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45595</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45097</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45284</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45585</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>44818</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>44818</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45190</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45418</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45652</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45728</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45440</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45415</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45782</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45406</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45350</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>44846</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45390</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45237</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45645</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45784</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45876</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46139</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45726</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>44985</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45842</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45894</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45570</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45743</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>46191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45418</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>44924</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46246</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45712</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>45265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45402</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44797</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44942</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45183</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45393</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45477</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45336</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45096</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44841</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>44928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45425</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45446</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44968</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45439</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45336</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44968</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44939</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45233</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45439</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45233</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44964</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44935</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45524</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45567</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44857</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45439</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44550</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45166</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45335</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45567</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45264</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45628</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46114</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>46057</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45233</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45673</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46062</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>46239</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44915</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44833</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45366</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44647</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44516</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46129</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45673</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45040</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45378</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45183</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44508</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44496</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45477</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>46008</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45301</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45665</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>46209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45467</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44609</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45477</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44628</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44771</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44678</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45448</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44725</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>44508</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45335</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45212</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45338</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44924</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45467</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44821</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45097</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45700</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46048</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>44934</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44847</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45363</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45582</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45302</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45526</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45830</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45595</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44755</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45072</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44839</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44530</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>46203</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45305</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44504</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>46125</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>46148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45720</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45379</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45403</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45687</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>45159</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45688</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44839</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44674</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44725</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44713</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44725</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44496</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44487</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>44538</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>44713</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>44841</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44876</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44515</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44652</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44647</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>44647</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45039</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45265</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45301</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45086</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45322</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44881</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45441</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45368</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45240</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44968</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45667</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45597</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44699</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45852</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>45222</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>46009</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44959</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45852</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45327</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>44698</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>46024</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45891</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45521</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45653</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45638</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45691</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45793</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45743</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45700</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>46048</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>46048</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>46048</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45207</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45461</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45806</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45928</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45443</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45418</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>46062</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45475</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45337</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45856</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45939</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>46071</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>46071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>46083</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>46040</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45058</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45260</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45301</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45499</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45179</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45000</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>44609</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45706</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>46008</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44516</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45635</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45730</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45079</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44760</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45349</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44624</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45709</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45102</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45822</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45868</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45722</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46128</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45183</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45173</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45632</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>46008</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45807</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45804</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45750</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45397</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45349</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45673</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44955</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45541</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45737</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45575</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45852</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45013</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45278</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45705</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45705</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>45647</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45401</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45514</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45772</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46057</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44881</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45823</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44882</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45669</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45670</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>44897</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45837</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45335</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45680</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45132</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45491</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45706</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45672</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45830</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>45571</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45763</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45852</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44998</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45314</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45363</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45177</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46154</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46154</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46154</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45539</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45852</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>44841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45029</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44741</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44936</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45695</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45779</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45698</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45764</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45774</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45407</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>44833</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45733</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45561</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46184</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>44705</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>44682</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45274</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45615</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44855</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>45076</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45183</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45281</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>44929</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>44929</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45301</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>44963</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45601</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45336</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45161</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45418</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45213</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45733</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46213</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>46213</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46218</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>44988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45376</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45282</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46226</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46226</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46268</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>45705</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44955</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45187</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45415</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45197</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46237</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46239</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46282</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46240</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45072</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45477</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45607</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45791</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45671</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>45491</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44944</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44988</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>46188</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46154</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45709</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46188</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46160</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46292</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46076</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45602</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45576</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45163</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45895</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>46293</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>44944</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45072</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>44938</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45180</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45764</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45370</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>44699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>44959</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45695</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45695</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45071</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46071</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>46071</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46071</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44733</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46195</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45716</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>44909</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45509</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45056</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45394</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45595</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45097</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45284</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45585</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>44818</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>44818</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45190</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45418</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45652</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45728</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45440</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45415</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45782</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45406</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45350</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>44846</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45390</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45237</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45645</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45784</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45876</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46139</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45726</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>44985</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46191</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45570</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45743</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>45939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45299</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45418</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44924</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45743</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45712</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45402</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4976,10 +4976,10 @@
         <v>17</v>
       </c>
       <c r="T34" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="U34" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44480</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44942</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44797</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>45183</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45371</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6428,10 +6428,10 @@
         <v>14</v>
       </c>
       <c r="T46" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="U46" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>46010</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>45336</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44949</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>45477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45179</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7262,10 +7262,10 @@
         <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="U53" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45418</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45096</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>46044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45691</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>45425</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44841</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45622</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44968</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45439</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45336</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45233</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44939</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44968</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45233</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>46071</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46071</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>44964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45720</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45524</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>46010</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45567</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>44857</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45183</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44510</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45939</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45439</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>46226</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45701</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45335</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45166</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45183</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45567</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45980</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44040</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45628</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>44936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45264</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45692</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45233</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>46114</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45040</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45366</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>44647</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45183</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45673</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45378</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>44833</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46129</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46185</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45695</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44839</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44698</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45301</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45477</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44609</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45840</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45477</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>46084</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45665</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>46190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>46260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45198</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>44678</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>44628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45379</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44934</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44725</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45595</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44504</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45335</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45212</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45305</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45705</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45687</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45338</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45403</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44968</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44508</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>44821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45526</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45302</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45524</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45363</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>44986</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44924</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44839</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45212</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45830</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>46048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44530</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45072</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45097</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46125</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>46148</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>44511</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23616,10 +23616,10 @@
         <v>1</v>
       </c>
       <c r="T203" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U203" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V203" s="2" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45159</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44889</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44824</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45688</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>46202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44839</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44674</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44725</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>44713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44725</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44496</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>44713</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44487</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44841</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44652</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44876</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44515</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>44538</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44647</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44647</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>44483</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>44733</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45183</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>44741</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45072</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45670</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45078</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45370</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45475</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45086</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45079</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45743</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45734</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44959</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44760</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>44839</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44968</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45250</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45301</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45443</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45213</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44841</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45203</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45301</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45207</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45071</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45102</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44516</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45183</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45190</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45680</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45363</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45418</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44896</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>44699</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45539</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45322</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45575</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45314</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45733</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45852</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45852</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45491</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44959</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44938</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45891</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45499</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45013</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45337</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45638</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45706</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45615</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45695</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45521</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45576</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45477</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45349</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45647</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44974</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45284</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45593</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45415</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45782</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45336</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>44881</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45407</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45173</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45418</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45349</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45240</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45368</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45394</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45103</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45441</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45806</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45509</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45928</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45335</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45585</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45793</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45595</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45693</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45709</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>45705</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45667</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44818</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45856</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>44855</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>45597</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>45197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45931</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45440</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>44897</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44609</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45112</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45939</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45072</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44968</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45652</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45706</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45278</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45709</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>44698</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45822</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45728</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>45183</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45632</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45415</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45671</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45056</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45000</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45672</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44998</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44929</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45750</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45161</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45602</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45669</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45180</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45852</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45187</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45514</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45722</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45029</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45978</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45744</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45571</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45830</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45758</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44987</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45763</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45852</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>44988</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45691</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45301</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45070</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45730</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45695</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45695</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>45397</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45698</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45779</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45265</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>45212</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45764</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44496</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45774</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>45039</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45541</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>46008</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>44712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44881</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45197</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45418</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45705</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45601</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>44682</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>44909</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45376</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45561</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45264</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45282</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45823</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45804</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45673</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45772</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45837</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44955</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>44955</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46035</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46009</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45737</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>46000</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45607</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>44931</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46024</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46057</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45161</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>44963</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45764</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>44944</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44988</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>44944</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>46036</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45716</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45461</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>44966</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>46048</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44705</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44929</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>46048</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44944</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>46048</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45327</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45222</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44882</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>46062</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>46036</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>46071</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>46071</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>46154</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46154</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>46154</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46040</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45852</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>46009</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46170</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46213</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>46213</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>46218</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>46226</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>46268</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>46237</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46239</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>46282</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46286</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46240</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45791</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46154</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>46188</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>46188</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>46076</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>46293</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>46292</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45895</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>46300</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>46008</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>46298</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>46280</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>46198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>46301</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>46301</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45406</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45350</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45209</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44846</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45390</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45237</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45645</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45784</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45876</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>46139</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45726</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46149</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>44985</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46191</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45570</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2331,75 +2331,210 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
+          <t>A 6153-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>27</v>
+      </c>
+      <c r="R14" t="n">
+        <v>15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>31</v>
+      </c>
+      <c r="T14" t="n">
+        <v>95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>95</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartnande fingersvamp
+Bredbrämad bastardsvärmare
+Granrotspindling
+Gul lammticka
+Gulsträngad fagerspindling
+Ljungsnärja
+Läderdoftande fingersvamp
+Mörkfjällig olivspindling
+Narrspindling
+Sexfläckig bastardsvärmare
+Solvändesäckmal
+Svartfläckig blåvinge
+Svartgrön spindling
+Violettfläckig spindling
+Backtimjan
+Blå slemspindling
+Brokigt timjansmott
+Fjällig taggsvamp s.str.
+Jordtistel
+Kryddspindling
+Mindre tåtelsmygare
+Odörspindling
+Sandkremla
+Slåtterfibbla
+Solvända
+Svinrot
+Anisspindling
+Mindre märgborre
+Murgröna
+Olivspindling</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 6153-2024 artfynd.xlsx", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 6153-2024 karta.png", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 6153-2024 georefererad karta.tif", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 6153-2024 FSC-klagomål.docx", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 6153-2024 FSC-klagomål mail.docx", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 6153-2024 tillsynsbegäran.docx", "A 6153-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 6153-2024 tillsynsbegäran mail.docx", "A 6153-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>A 15075-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45743</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>20.9</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>9</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>8</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>9</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>18</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>10</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>30</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>131</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>131</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Violgubbe
 Bananspindling
@@ -2433,111 +2568,111 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 15075-2025 artfynd.xlsx", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 15075-2025 karta.png", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 15075-2025 georefererad karta.tif", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 15075-2025 FSC-klagomål.docx", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 15075-2025 FSC-klagomål mail.docx", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 15075-2025 tillsynsbegäran.docx", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 15075-2025 tillsynsbegäran mail.docx", "A 15075-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 15075-2025 prioriterade fågelarter.docx", "A 15075-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>S 2823-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45939</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>87</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>10</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>11</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>21</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>11</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>30</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>121</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Blåfotad fagerspindling
 Bullspindling
@@ -2571,111 +2706,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/S 2823-2025 artfynd.xlsx", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/S 2823-2025 karta.png", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/S 2823-2025 georefererad karta.tif", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/S 2823-2025 FSC-klagomål.docx", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/S 2823-2025 FSC-klagomål mail.docx", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/S 2823-2025 tillsynsbegäran.docx", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/S 2823-2025 tillsynsbegäran mail.docx", "S 2823-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/S 2823-2025 prioriterade fågelarter.docx", "S 2823-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 45536-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45922</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>10.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>10</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>8</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>21</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>10</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>29</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>92</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>91</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Slät taggsvamp
 Sotbandad spindling
@@ -2708,168 +2843,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 45536-2025 artfynd.xlsx", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 45536-2025 karta.png", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 45536-2025 georefererad karta.tif", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 45536-2025 FSC-klagomål.docx", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 45536-2025 FSC-klagomål mail.docx", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 45536-2025 tillsynsbegäran.docx", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 45536-2025 tillsynsbegäran mail.docx", "A 45536-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 45536-2025 prioriterade fågelarter.docx", "A 45536-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 6153-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45337</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" t="n">
-        <v>12</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>24</v>
-      </c>
-      <c r="R17" t="n">
-        <v>14</v>
-      </c>
-      <c r="S17" t="n">
-        <v>28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>68</v>
-      </c>
-      <c r="U17" t="n">
-        <v>68</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartnande fingersvamp
-Bredbrämad bastardsvärmare
-Gul lammticka
-Gulsträngad fagerspindling
-Ljungsnärja
-Läderdoftande fingersvamp
-Mörkfjällig olivspindling
-Narrspindling
-Sexfläckig bastardsvärmare
-Solvändesäckmal
-Svartfläckig blåvinge
-Svartgrön spindling
-Violettfläckig spindling
-Backtimjan
-Blå slemspindling
-Brokigt timjansmott
-Jordtistel
-Kryddspindling
-Mindre tåtelsmygare
-Odörspindling
-Slåtterfibbla
-Solvända
-Svinrot
-Anisspindling
-Mindre märgborre
-Murgröna
-Olivspindling</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 6153-2024 artfynd.xlsx", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 6153-2024 karta.png", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 6153-2024 georefererad karta.tif", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 6153-2024 FSC-klagomål.docx", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 6153-2024 FSC-klagomål mail.docx", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 6153-2024 tillsynsbegäran.docx", "A 6153-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 6153-2024 tillsynsbegäran mail.docx", "A 6153-2024")</f>
         <v/>
       </c>
     </row>
@@ -2893,7 +2896,7 @@
         <v>44932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3025,7 +3028,7 @@
         <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3157,7 +3160,7 @@
         <v>45299</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3288,7 +3291,7 @@
         <v>45309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3423,7 +3426,7 @@
         <v>45418</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3549,7 +3552,7 @@
         <v>44924</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3674,7 +3677,7 @@
         <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3803,7 +3806,7 @@
         <v>44935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3931,7 +3934,7 @@
         <v>45743</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4054,7 +4057,7 @@
         <v>45712</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4181,7 +4184,7 @@
         <v>45265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4308,7 +4311,7 @@
         <v>45402</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4434,7 +4437,7 @@
         <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4556,7 +4559,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4678,7 +4681,7 @@
         <v>44509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4804,7 +4807,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4930,7 +4933,7 @@
         <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5055,7 +5058,7 @@
         <v>45265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5176,7 +5179,7 @@
         <v>44480</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5297,7 +5300,7 @@
         <v>44942</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5417,7 +5420,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5541,7 +5544,7 @@
         <v>44797</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5661,7 +5664,7 @@
         <v>44839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5785,7 +5788,7 @@
         <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5905,7 +5908,7 @@
         <v>45183</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6024,7 +6027,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6146,7 +6149,7 @@
         <v>44841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6264,7 +6267,7 @@
         <v>45371</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6382,7 +6385,7 @@
         <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6504,7 +6507,7 @@
         <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6626,7 +6629,7 @@
         <v>44741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6743,7 +6746,7 @@
         <v>46010</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6864,7 +6867,7 @@
         <v>45336</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6980,7 +6983,7 @@
         <v>44949</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7096,7 +7099,7 @@
         <v>45477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7216,7 +7219,7 @@
         <v>45179</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7332,7 +7335,7 @@
         <v>45418</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7448,7 +7451,7 @@
         <v>44930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7563,7 +7566,7 @@
         <v>45096</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7682,7 +7685,7 @@
         <v>44943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7797,7 +7800,7 @@
         <v>46044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7912,7 +7915,7 @@
         <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8030,7 +8033,7 @@
         <v>44928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8144,7 +8147,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8262,7 +8265,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8376,7 +8379,7 @@
         <v>45691</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8494,7 +8497,7 @@
         <v>45425</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8613,7 +8616,7 @@
         <v>44841</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8727,7 +8730,7 @@
         <v>45622</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8841,7 +8844,7 @@
         <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8955,7 +8958,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9068,7 +9071,7 @@
         <v>44968</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9181,7 +9184,7 @@
         <v>45439</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9298,7 +9301,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9420,7 +9423,7 @@
         <v>45336</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9538,7 +9541,7 @@
         <v>45233</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9654,7 +9657,7 @@
         <v>44939</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9766,7 +9769,7 @@
         <v>44968</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9878,7 +9881,7 @@
         <v>45233</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9994,7 +9997,7 @@
         <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10106,7 +10109,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10218,7 +10221,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10334,7 +10337,7 @@
         <v>46071</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10446,7 +10449,7 @@
         <v>46071</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10558,7 +10561,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10670,7 +10673,7 @@
         <v>44964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10781,7 +10784,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10892,7 +10895,7 @@
         <v>45720</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11003,7 +11006,7 @@
         <v>44939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11114,7 +11117,7 @@
         <v>45524</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11225,7 +11228,7 @@
         <v>45854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11336,7 +11339,7 @@
         <v>46010</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11451,7 +11454,7 @@
         <v>45567</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11562,7 +11565,7 @@
         <v>44857</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11676,7 +11679,7 @@
         <v>45183</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11786,7 +11789,7 @@
         <v>44510</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11896,7 +11899,7 @@
         <v>45939</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12010,7 +12013,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12124,7 +12127,7 @@
         <v>45439</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12238,7 +12241,7 @@
         <v>46226</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12348,7 +12351,7 @@
         <v>45701</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12463,7 +12466,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12572,7 +12575,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12681,7 +12684,7 @@
         <v>45335</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12790,7 +12793,7 @@
         <v>45166</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12903,7 +12906,7 @@
         <v>44881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13012,7 +13015,7 @@
         <v>45183</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13121,7 +13124,7 @@
         <v>45567</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13230,7 +13233,7 @@
         <v>45980</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13337,7 +13340,7 @@
         <v>44040</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13446,7 +13449,7 @@
         <v>45628</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13554,7 +13557,7 @@
         <v>44936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13662,7 +13665,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13770,7 +13773,7 @@
         <v>44915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13878,7 +13881,7 @@
         <v>45673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13986,7 +13989,7 @@
         <v>45264</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14094,7 +14097,7 @@
         <v>45692</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14202,7 +14205,7 @@
         <v>45233</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14310,7 +14313,7 @@
         <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14422,7 +14425,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14530,7 +14533,7 @@
         <v>46114</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14638,7 +14641,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14746,7 +14749,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14858,7 +14861,7 @@
         <v>45531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14965,7 +14968,7 @@
         <v>45040</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15072,7 +15075,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15179,7 +15182,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15286,7 +15289,7 @@
         <v>45366</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15397,7 +15400,7 @@
         <v>44647</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15508,7 +15511,7 @@
         <v>45183</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15615,7 +15618,7 @@
         <v>45673</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15722,7 +15725,7 @@
         <v>45378</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15829,7 +15832,7 @@
         <v>44833</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15936,7 +15939,7 @@
         <v>45205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16043,7 +16046,7 @@
         <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16150,7 +16153,7 @@
         <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16257,7 +16260,7 @@
         <v>46129</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16368,7 +16371,7 @@
         <v>46185</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16475,7 +16478,7 @@
         <v>45695</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16582,7 +16585,7 @@
         <v>44839</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16688,7 +16691,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16794,7 +16797,7 @@
         <v>44698</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16900,7 +16903,7 @@
         <v>45301</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17006,7 +17009,7 @@
         <v>45595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17112,7 +17115,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17218,7 +17221,7 @@
         <v>45477</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17324,7 +17327,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17430,7 +17433,7 @@
         <v>44609</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17540,7 +17543,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17646,7 +17649,7 @@
         <v>45840</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17756,7 +17759,7 @@
         <v>45477</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17862,7 +17865,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17973,7 +17976,7 @@
         <v>46084</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18079,7 +18082,7 @@
         <v>45665</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18185,7 +18188,7 @@
         <v>46190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18295,7 +18298,7 @@
         <v>46260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18405,7 +18408,7 @@
         <v>45198</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18511,7 +18514,7 @@
         <v>44678</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18616,7 +18619,7 @@
         <v>44628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18721,7 +18724,7 @@
         <v>44771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18826,7 +18829,7 @@
         <v>45379</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18931,7 +18934,7 @@
         <v>44929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19036,7 +19039,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19141,7 +19144,7 @@
         <v>44934</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19246,7 +19249,7 @@
         <v>44725</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19351,7 +19354,7 @@
         <v>45595</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19456,7 +19459,7 @@
         <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19561,7 +19564,7 @@
         <v>44504</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19666,7 +19669,7 @@
         <v>45335</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19771,7 +19774,7 @@
         <v>45212</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19876,7 +19879,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19981,7 +19984,7 @@
         <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20086,7 +20089,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20191,7 +20194,7 @@
         <v>45305</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20296,7 +20299,7 @@
         <v>44938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20401,7 +20404,7 @@
         <v>45705</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20506,7 +20509,7 @@
         <v>45687</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20611,7 +20614,7 @@
         <v>44917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20716,7 +20719,7 @@
         <v>45338</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20821,7 +20824,7 @@
         <v>44755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20926,7 +20929,7 @@
         <v>45403</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21031,7 +21034,7 @@
         <v>44968</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21136,7 +21139,7 @@
         <v>45700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21245,7 +21248,7 @@
         <v>44508</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21355,7 +21358,7 @@
         <v>44821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21460,7 +21463,7 @@
         <v>45526</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21565,7 +21568,7 @@
         <v>45302</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21670,7 +21673,7 @@
         <v>45524</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21775,7 +21778,7 @@
         <v>45363</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21880,7 +21883,7 @@
         <v>44986</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21985,7 +21988,7 @@
         <v>44924</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22090,7 +22093,7 @@
         <v>44839</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22195,7 +22198,7 @@
         <v>45212</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22300,7 +22303,7 @@
         <v>45830</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22405,7 +22408,7 @@
         <v>46048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22510,7 +22513,7 @@
         <v>44530</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22615,7 +22618,7 @@
         <v>45072</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22725,7 +22728,7 @@
         <v>45097</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22830,7 +22833,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22935,7 +22938,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23040,7 +23043,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23145,7 +23148,7 @@
         <v>46125</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23250,7 +23253,7 @@
         <v>46148</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23355,7 +23358,7 @@
         <v>44511</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23465,7 +23468,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23570,7 +23573,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23675,7 +23678,7 @@
         <v>45159</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23780,7 +23783,7 @@
         <v>44889</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23885,7 +23888,7 @@
         <v>44824</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23990,7 +23993,7 @@
         <v>45688</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24095,7 +24098,7 @@
         <v>46202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24200,7 +24203,7 @@
         <v>44839</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24273,7 +24276,7 @@
         <v>44674</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24346,7 +24349,7 @@
         <v>44725</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24419,7 +24422,7 @@
         <v>44713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24492,7 +24495,7 @@
         <v>44725</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24565,7 +24568,7 @@
         <v>44496</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24638,7 +24641,7 @@
         <v>44713</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24711,7 +24714,7 @@
         <v>44487</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24784,7 +24787,7 @@
         <v>44841</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -24857,7 +24860,7 @@
         <v>44652</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24930,7 +24933,7 @@
         <v>44876</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25008,7 +25011,7 @@
         <v>44515</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25081,7 +25084,7 @@
         <v>44538</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25154,7 +25157,7 @@
         <v>44647</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25227,7 +25230,7 @@
         <v>44647</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25300,7 +25303,7 @@
         <v>44483</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25378,7 +25381,7 @@
         <v>44936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25451,7 +25454,7 @@
         <v>44733</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25524,7 +25527,7 @@
         <v>45183</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25597,7 +25600,7 @@
         <v>44741</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -25675,7 +25678,7 @@
         <v>45072</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -25748,7 +25751,7 @@
         <v>45670</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -25821,7 +25824,7 @@
         <v>45078</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25899,7 +25902,7 @@
         <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25972,7 +25975,7 @@
         <v>45370</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26045,7 +26048,7 @@
         <v>45475</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26118,7 +26121,7 @@
         <v>45086</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26191,7 +26194,7 @@
         <v>45079</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26264,7 +26267,7 @@
         <v>45743</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26337,7 +26340,7 @@
         <v>45734</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26410,7 +26413,7 @@
         <v>44959</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26483,7 +26486,7 @@
         <v>44760</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26556,7 +26559,7 @@
         <v>44839</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -26629,7 +26632,7 @@
         <v>44968</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -26702,7 +26705,7 @@
         <v>45058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -26775,7 +26778,7 @@
         <v>45250</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26848,7 +26851,7 @@
         <v>45301</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26921,7 +26924,7 @@
         <v>45443</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26994,7 +26997,7 @@
         <v>45213</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27067,7 +27070,7 @@
         <v>44841</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27140,7 +27143,7 @@
         <v>45203</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27213,7 +27216,7 @@
         <v>45301</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27286,7 +27289,7 @@
         <v>44909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27359,7 +27362,7 @@
         <v>45207</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27432,7 +27435,7 @@
         <v>45071</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27505,7 +27508,7 @@
         <v>45102</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27578,7 +27581,7 @@
         <v>44516</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -27651,7 +27654,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -27724,7 +27727,7 @@
         <v>45183</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27797,7 +27800,7 @@
         <v>45190</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27870,7 +27873,7 @@
         <v>45680</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27943,7 +27946,7 @@
         <v>45363</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28016,7 +28019,7 @@
         <v>45418</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28089,7 +28092,7 @@
         <v>44896</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28162,7 +28165,7 @@
         <v>44699</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28240,7 +28243,7 @@
         <v>45539</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28313,7 +28316,7 @@
         <v>45197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28386,7 +28389,7 @@
         <v>45322</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28459,7 +28462,7 @@
         <v>45274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28532,7 +28535,7 @@
         <v>45575</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -28605,7 +28608,7 @@
         <v>45314</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -28678,7 +28681,7 @@
         <v>45733</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -28751,7 +28754,7 @@
         <v>45852</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28824,7 +28827,7 @@
         <v>45852</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28897,7 +28900,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28970,7 +28973,7 @@
         <v>45491</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29043,7 +29046,7 @@
         <v>44959</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29116,7 +29119,7 @@
         <v>44938</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29189,7 +29192,7 @@
         <v>45891</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29262,7 +29265,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29335,7 +29338,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29413,7 +29416,7 @@
         <v>45499</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29486,7 +29489,7 @@
         <v>45013</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29559,7 +29562,7 @@
         <v>45337</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -29632,7 +29635,7 @@
         <v>45638</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -29705,7 +29708,7 @@
         <v>45706</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29778,7 +29781,7 @@
         <v>45615</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29851,7 +29854,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29924,7 +29927,7 @@
         <v>45695</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29997,7 +30000,7 @@
         <v>45521</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30070,7 +30073,7 @@
         <v>45576</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30143,7 +30146,7 @@
         <v>45477</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30216,7 +30219,7 @@
         <v>45349</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30289,7 +30292,7 @@
         <v>45647</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30362,7 +30365,7 @@
         <v>44974</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30435,7 +30438,7 @@
         <v>45284</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30508,7 +30511,7 @@
         <v>45593</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30581,7 +30584,7 @@
         <v>45415</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -30654,7 +30657,7 @@
         <v>45782</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30727,7 +30730,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30800,7 +30803,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30873,7 +30876,7 @@
         <v>45336</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30946,7 +30949,7 @@
         <v>44881</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31019,7 +31022,7 @@
         <v>45407</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31092,7 +31095,7 @@
         <v>45173</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31165,7 +31168,7 @@
         <v>45418</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31238,7 +31241,7 @@
         <v>45349</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31311,7 +31314,7 @@
         <v>45240</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31384,7 +31387,7 @@
         <v>45368</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31457,7 +31460,7 @@
         <v>45394</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31530,7 +31533,7 @@
         <v>45103</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -31603,7 +31606,7 @@
         <v>45441</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -31676,7 +31679,7 @@
         <v>45806</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31749,7 +31752,7 @@
         <v>45509</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31822,7 +31825,7 @@
         <v>45928</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31895,7 +31898,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31968,7 +31971,7 @@
         <v>45147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32041,7 +32044,7 @@
         <v>45335</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32114,7 +32117,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32187,7 +32190,7 @@
         <v>44936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32260,7 +32263,7 @@
         <v>45585</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32333,7 +32336,7 @@
         <v>45793</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32406,7 +32409,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32479,7 +32482,7 @@
         <v>44624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32552,7 +32555,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -32625,7 +32628,7 @@
         <v>45595</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32698,7 +32701,7 @@
         <v>44944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32771,7 +32774,7 @@
         <v>45693</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32844,7 +32847,7 @@
         <v>45709</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32917,7 +32920,7 @@
         <v>45705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32990,7 +32993,7 @@
         <v>45705</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33063,7 +33066,7 @@
         <v>45667</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33136,7 +33139,7 @@
         <v>44818</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33209,7 +33212,7 @@
         <v>45856</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33282,7 +33285,7 @@
         <v>44699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33360,7 +33363,7 @@
         <v>44855</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33433,7 +33436,7 @@
         <v>45597</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33506,7 +33509,7 @@
         <v>45197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -33579,7 +33582,7 @@
         <v>45931</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -33652,7 +33655,7 @@
         <v>45440</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33725,7 +33728,7 @@
         <v>44897</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33798,7 +33801,7 @@
         <v>44609</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33871,7 +33874,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33944,7 +33947,7 @@
         <v>45112</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34017,7 +34020,7 @@
         <v>45939</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34090,7 +34093,7 @@
         <v>45072</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34163,7 +34166,7 @@
         <v>44968</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34236,7 +34239,7 @@
         <v>45652</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34309,7 +34312,7 @@
         <v>45076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34382,7 +34385,7 @@
         <v>45706</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34455,7 +34458,7 @@
         <v>45278</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34528,7 +34531,7 @@
         <v>45709</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -34601,7 +34604,7 @@
         <v>44698</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34674,7 +34677,7 @@
         <v>45822</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34747,7 +34750,7 @@
         <v>45728</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34820,7 +34823,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34893,7 +34896,7 @@
         <v>45183</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34966,7 +34969,7 @@
         <v>45632</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35039,7 +35042,7 @@
         <v>45415</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35112,7 +35115,7 @@
         <v>45671</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35185,7 +35188,7 @@
         <v>45056</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35258,7 +35261,7 @@
         <v>45000</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35331,7 +35334,7 @@
         <v>45672</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35404,7 +35407,7 @@
         <v>44998</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35477,7 +35480,7 @@
         <v>44929</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35550,7 +35553,7 @@
         <v>44929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35623,7 +35626,7 @@
         <v>45750</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35696,7 +35699,7 @@
         <v>45161</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35769,7 +35772,7 @@
         <v>45602</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35842,7 +35845,7 @@
         <v>45669</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35915,7 +35918,7 @@
         <v>45180</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35988,7 +35991,7 @@
         <v>45852</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36061,7 +36064,7 @@
         <v>45187</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36134,7 +36137,7 @@
         <v>45514</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36207,7 +36210,7 @@
         <v>45722</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36280,7 +36283,7 @@
         <v>45029</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36353,7 +36356,7 @@
         <v>45978</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36426,7 +36429,7 @@
         <v>45744</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36499,7 +36502,7 @@
         <v>45571</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36572,7 +36575,7 @@
         <v>45743</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36645,7 +36648,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36718,7 +36721,7 @@
         <v>45830</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36796,7 +36799,7 @@
         <v>45758</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36869,7 +36872,7 @@
         <v>44987</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36942,7 +36945,7 @@
         <v>45763</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37015,7 +37018,7 @@
         <v>45852</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37088,7 +37091,7 @@
         <v>44988</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37166,7 +37169,7 @@
         <v>45691</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37239,7 +37242,7 @@
         <v>45301</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37312,7 +37315,7 @@
         <v>45070</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37385,7 +37388,7 @@
         <v>45730</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37458,7 +37461,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37531,7 +37534,7 @@
         <v>45695</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37604,7 +37607,7 @@
         <v>45695</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37677,7 +37680,7 @@
         <v>45397</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37750,7 +37753,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37823,7 +37826,7 @@
         <v>45698</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37896,7 +37899,7 @@
         <v>45779</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37969,7 +37972,7 @@
         <v>45265</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38042,7 +38045,7 @@
         <v>45212</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38115,7 +38118,7 @@
         <v>45764</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38188,7 +38191,7 @@
         <v>44496</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38261,7 +38264,7 @@
         <v>45774</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38334,7 +38337,7 @@
         <v>45039</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38412,7 +38415,7 @@
         <v>45541</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38485,7 +38488,7 @@
         <v>46008</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38563,7 +38566,7 @@
         <v>44712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38636,7 +38639,7 @@
         <v>44881</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38709,7 +38712,7 @@
         <v>45197</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38782,7 +38785,7 @@
         <v>45290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38855,7 +38858,7 @@
         <v>45418</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38928,7 +38931,7 @@
         <v>45705</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39001,7 +39004,7 @@
         <v>45601</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39074,7 +39077,7 @@
         <v>44682</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39147,7 +39150,7 @@
         <v>44909</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39220,7 +39223,7 @@
         <v>45376</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39293,7 +39296,7 @@
         <v>45561</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39366,7 +39369,7 @@
         <v>45264</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39439,7 +39442,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39517,7 +39520,7 @@
         <v>45281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39590,7 +39593,7 @@
         <v>45282</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39663,7 +39666,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39736,7 +39739,7 @@
         <v>45823</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39809,7 +39812,7 @@
         <v>45804</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39882,7 +39885,7 @@
         <v>45673</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39955,7 +39958,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40033,7 +40036,7 @@
         <v>45772</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40106,7 +40109,7 @@
         <v>45837</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40179,7 +40182,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40252,7 +40255,7 @@
         <v>44955</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40330,7 +40333,7 @@
         <v>44955</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40403,7 +40406,7 @@
         <v>46035</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40476,7 +40479,7 @@
         <v>46009</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40549,7 +40552,7 @@
         <v>45737</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40627,7 +40630,7 @@
         <v>44818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40700,7 +40703,7 @@
         <v>46000</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40773,7 +40776,7 @@
         <v>45607</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40846,7 +40849,7 @@
         <v>44931</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40919,7 +40922,7 @@
         <v>46024</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40992,7 +40995,7 @@
         <v>46057</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41070,7 +41073,7 @@
         <v>45161</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41143,7 +41146,7 @@
         <v>44963</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41216,7 +41219,7 @@
         <v>45764</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41289,7 +41292,7 @@
         <v>44944</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41362,7 +41365,7 @@
         <v>44988</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41440,7 +41443,7 @@
         <v>44944</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41513,7 +41516,7 @@
         <v>46036</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41586,7 +41589,7 @@
         <v>45177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41659,7 +41662,7 @@
         <v>45716</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41732,7 +41735,7 @@
         <v>45097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41805,7 +41808,7 @@
         <v>45461</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41878,7 +41881,7 @@
         <v>44966</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41951,7 +41954,7 @@
         <v>46048</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42024,7 +42027,7 @@
         <v>44705</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42097,7 +42100,7 @@
         <v>44929</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42170,7 +42173,7 @@
         <v>46048</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42243,7 +42246,7 @@
         <v>44944</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42316,7 +42319,7 @@
         <v>46048</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42389,7 +42392,7 @@
         <v>45327</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42462,7 +42465,7 @@
         <v>45222</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42535,7 +42538,7 @@
         <v>44882</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42608,7 +42611,7 @@
         <v>46062</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42681,7 +42684,7 @@
         <v>46036</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42754,7 +42757,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42827,7 +42830,7 @@
         <v>46071</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42900,7 +42903,7 @@
         <v>46071</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42973,7 +42976,7 @@
         <v>46154</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43046,7 +43049,7 @@
         <v>46154</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43119,7 +43122,7 @@
         <v>46154</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43192,7 +43195,7 @@
         <v>46040</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43265,7 +43268,7 @@
         <v>45852</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43343,7 +43346,7 @@
         <v>46009</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43421,7 +43424,7 @@
         <v>46170</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43494,7 +43497,7 @@
         <v>46184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43567,7 +43570,7 @@
         <v>46213</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43640,7 +43643,7 @@
         <v>46213</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43713,7 +43716,7 @@
         <v>46218</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43786,7 +43789,7 @@
         <v>46226</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43859,7 +43862,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43937,7 +43940,7 @@
         <v>46268</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44015,7 +44018,7 @@
         <v>46237</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44088,7 +44091,7 @@
         <v>46239</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44161,7 +44164,7 @@
         <v>46282</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44234,7 +44237,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44307,7 +44310,7 @@
         <v>46286</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44380,7 +44383,7 @@
         <v>46240</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44453,7 +44456,7 @@
         <v>45791</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44526,7 +44529,7 @@
         <v>46154</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44599,7 +44602,7 @@
         <v>46160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44672,7 +44675,7 @@
         <v>46163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44745,7 +44748,7 @@
         <v>46188</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44818,7 +44821,7 @@
         <v>46188</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44891,7 +44894,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44964,7 +44967,7 @@
         <v>46076</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45037,7 +45040,7 @@
         <v>46293</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45110,7 +45113,7 @@
         <v>46292</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45183,7 +45186,7 @@
         <v>45895</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45256,7 +45259,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45329,7 +45332,7 @@
         <v>46300</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45402,7 +45405,7 @@
         <v>46008</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45475,7 +45478,7 @@
         <v>46298</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45548,7 +45551,7 @@
         <v>46280</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45621,7 +45624,7 @@
         <v>46198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45694,7 +45697,7 @@
         <v>46301</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45767,7 +45770,7 @@
         <v>46301</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45840,7 +45843,7 @@
         <v>45406</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45913,7 +45916,7 @@
         <v>45350</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45986,7 +45989,7 @@
         <v>45209</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46059,7 +46062,7 @@
         <v>44846</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46132,7 +46135,7 @@
         <v>45390</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46205,7 +46208,7 @@
         <v>45237</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46278,7 +46281,7 @@
         <v>45645</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46351,7 +46354,7 @@
         <v>45784</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46424,7 +46427,7 @@
         <v>45876</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46497,7 +46500,7 @@
         <v>46139</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46570,7 +46573,7 @@
         <v>45726</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46643,7 +46646,7 @@
         <v>46149</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>

--- a/Översikt GOTLAND.xlsx
+++ b/Översikt GOTLAND.xlsx
@@ -601,7 +601,7 @@
         <v>45328</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45357</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44930</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45687</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45842</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44985</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45337</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45827</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45831</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>46246</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46191</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>45299</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45570</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>45743</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46307</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44964</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>44930</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44932</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45309</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46309</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45748</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 999-2023</t>
+          <t>A 1477-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44935</v>
+        <v>45305</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4514,22 +4514,22 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4538,21 +4538,154 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R30" t="n">
         <v>7</v>
       </c>
       <c r="S30" t="n">
+        <v>21</v>
+      </c>
+      <c r="T30" t="n">
+        <v>47</v>
+      </c>
+      <c r="U30" t="n">
+        <v>47</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Fågelträcksspindling
+Granrotspindling
+Igelkott
+Knärot
+Svartgrön spindling
+Vit taggsvamp
+Backtimjan
+Blå slemspindling
+Flattoppad klubbsvamp
+Odörspindling
+Sårläka
+Anisspindling
+Diskvaxskivling
+Grönpyrola
+Nästrot
+Purpurknipprot
+Skogsknipprot
+Svavelriska
+Kransmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 1477-2024 artfynd.xlsx", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 1477-2024 karta.png", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 1477-2024 georefererad karta.tif", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/knärot/A 1477-2024 karta knärot.png", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 1477-2024 FSC-klagomål.docx", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 1477-2024 FSC-klagomål mail.docx", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 1477-2024 tillsynsbegäran.docx", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 1477-2024 tillsynsbegäran mail.docx", "A 1477-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 1477-2024 prioriterade fågelarter.docx", "A 1477-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 999-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>44935</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>16</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" t="n">
         <v>20</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>120</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>120</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sienamusseron
@@ -4576,111 +4709,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 999-2023 artfynd.xlsx", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 999-2023 karta.png", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 999-2023 georefererad karta.tif", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 999-2023 FSC-klagomål.docx", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 999-2023 FSC-klagomål mail.docx", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 999-2023 tillsynsbegäran.docx", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 999-2023 tillsynsbegäran mail.docx", "A 999-2023")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 999-2023 prioriterade fågelarter.docx", "A 999-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 15068-2025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>45743</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E32" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>37.3</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>5</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>4</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>11</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>4</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>19</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>49</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>19</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Granrotspindling
 Gulsträngad fagerspindling
@@ -4703,107 +4836,107 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 15068-2025 artfynd.xlsx", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 15068-2025 karta.png", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 15068-2025 georefererad karta.tif", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 15068-2025 FSC-klagomål.docx", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 15068-2025 FSC-klagomål mail.docx", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 15068-2025 tillsynsbegäran.docx", "A 15068-2025")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 15068-2025 tillsynsbegäran mail.docx", "A 15068-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 8645-2025</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45712</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>21.9</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>7</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>6</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>19</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>97</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>97</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Ask
 Backtimjan
@@ -4826,111 +4959,111 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 8645-2025 artfynd.xlsx", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 8645-2025 karta.png", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 8645-2025 georefererad karta.tif", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 8645-2025 FSC-klagomål.docx", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 8645-2025 FSC-klagomål mail.docx", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 8645-2025 tillsynsbegäran.docx", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 8645-2025 tillsynsbegäran mail.docx", "A 8645-2025")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 8645-2025 prioriterade fågelarter.docx", "A 8645-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 61664-2023</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>4.8</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>6</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>7</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>8</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>3</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>19</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>59</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>48</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Klenodspindling
 Duvspindling
@@ -4953,111 +5086,111 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 61664-2023 artfynd.xlsx", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 61664-2023 karta.png", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 61664-2023 georefererad karta.tif", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 61664-2023 FSC-klagomål.docx", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 61664-2023 FSC-klagomål mail.docx", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 61664-2023 tillsynsbegäran.docx", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 61664-2023 tillsynsbegäran mail.docx", "A 61664-2023")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 61664-2023 prioriterade fågelarter.docx", "A 61664-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 63872-2021</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>44509</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>20.5</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>4</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>7</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>7</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>7</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>18</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>47</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U35" t="n">
         <v>36</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Duvspindling
 Gulsträngad fagerspindling
@@ -5079,111 +5212,111 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 63872-2021 artfynd.xlsx", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 63872-2021 karta.png", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 63872-2021 georefererad karta.tif", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 63872-2021 FSC-klagomål.docx", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 63872-2021 FSC-klagomål mail.docx", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 63872-2021 tillsynsbegäran.docx", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 63872-2021 tillsynsbegäran mail.docx", "A 63872-2021")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 63872-2021 prioriterade fågelarter.docx", "A 63872-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 15629-2024</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45402</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>6.3</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>6</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>10</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M36" t="n">
         <v>2</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>12</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>2</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>18</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>100</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>96</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Jordhår
 Solvändesäckmal
@@ -5205,111 +5338,111 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 15629-2024 artfynd.xlsx", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 15629-2024 karta.png", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 15629-2024 georefererad karta.tif", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 15629-2024 FSC-klagomål.docx", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 15629-2024 FSC-klagomål mail.docx", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 15629-2024 tillsynsbegäran.docx", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 15629-2024 tillsynsbegäran mail.docx", "A 15629-2024")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 15629-2024 prioriterade fågelarter.docx", "A 15629-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 59132-2024</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>45637</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="E37" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>3.5</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>3</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>8</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>2</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>13</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>4</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S37" t="n">
         <v>18</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>28</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>28</v>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Almlav
 Ask
@@ -5331,107 +5464,107 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 59132-2024 artfynd.xlsx", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 59132-2024 karta.png", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 59132-2024 georefererad karta.tif", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 59132-2024 FSC-klagomål.docx", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 59132-2024 FSC-klagomål mail.docx", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 59132-2024 tillsynsbegäran.docx", "A 59132-2024")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 59132-2024 tillsynsbegäran mail.docx", "A 59132-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 26987-2026</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D38" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="E38" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>4.6</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>6</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K38" t="n">
         <v>2</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L38" t="n">
         <v>11</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>13</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>2</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>18</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>52</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U38" t="n">
         <v>44</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Ask
 Granrotspindling
@@ -5453,111 +5586,111 @@
 Halsbandsflugsnappare</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 26987-2026 artfynd.xlsx", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 26987-2026 karta.png", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 26987-2026 georefererad karta.tif", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 26987-2026 FSC-klagomål.docx", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 26987-2026 FSC-klagomål mail.docx", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 26987-2026 tillsynsbegäran.docx", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 26987-2026 tillsynsbegäran mail.docx", "A 26987-2026")</f>
         <v/>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 26987-2026 prioriterade fågelarter.docx", "A 26987-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 7837-2024</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>45349</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+      <c r="E39" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>4</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>7</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>6</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>13</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>6</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>18</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>28</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>28</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Fågelträcksspindling
 Granrotspindling
@@ -5579,111 +5712,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 7837-2024 artfynd.xlsx", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 7837-2024 karta.png", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 7837-2024 georefererad karta.tif", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 7837-2024 FSC-klagomål.docx", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 7837-2024 FSC-klagomål mail.docx", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 7837-2024 tillsynsbegäran.docx", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 7837-2024 tillsynsbegäran mail.docx", "A 7837-2024")</f>
         <v/>
       </c>
-      <c r="AE38">
+      <c r="AE39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 7837-2024 prioriterade fågelarter.docx", "A 7837-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>A 39376-2023</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>45166</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
+      <c r="E40" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K40" t="n">
         <v>6</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L40" t="n">
         <v>9</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M40" t="n">
         <v>3</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>12</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S40" t="n">
         <v>18</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T40" t="n">
         <v>32</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U40" t="n">
         <v>32</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Granrotspindling
 Kopparspindling
@@ -5705,107 +5838,107 @@
 Svavelriska</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 39376-2023 artfynd.xlsx", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 39376-2023 karta.png", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 39376-2023 georefererad karta.tif", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 39376-2023 FSC-klagomål.docx", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 39376-2023 FSC-klagomål mail.docx", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 39376-2023 tillsynsbegäran.docx", "A 39376-2023")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 39376-2023 tillsynsbegäran mail.docx", "A 39376-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>A 61697-2023</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D41" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
+      <c r="E41" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>3</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>3</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>4</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>8</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N41" t="n">
         <v>1</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>13</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>9</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>17</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>41</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U41" t="n">
         <v>11</v>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Tallkejsarspindling
 Bullspindling
@@ -5826,107 +5959,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 61697-2023 artfynd.xlsx", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 61697-2023 karta.png", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 61697-2023 georefererad karta.tif", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 61697-2023 FSC-klagomål.docx", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 61697-2023 FSC-klagomål mail.docx", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 61697-2023 tillsynsbegäran.docx", "A 61697-2023")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 61697-2023 tillsynsbegäran mail.docx", "A 61697-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>A 62132-2023</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D42" s="1" t="n">
         <v>45267</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
+      <c r="E42" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
         <v>13.9</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>5</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>4</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L42" t="n">
         <v>7</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>4</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
         <v>11</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>4</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S42" t="n">
         <v>17</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>35</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U42" t="n">
         <v>21</v>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Granrotspindling
 Gulsträngad fagerspindling
@@ -5947,111 +6080,111 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 62132-2023 artfynd.xlsx", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 62132-2023 karta.png", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 62132-2023 georefererad karta.tif", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 62132-2023 FSC-klagomål.docx", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 62132-2023 FSC-klagomål mail.docx", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 62132-2023 tillsynsbegäran.docx", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 62132-2023 tillsynsbegäran mail.docx", "A 62132-2023")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 62132-2023 prioriterade fågelarter.docx", "A 62132-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>A 35141-2022</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D43" s="1" t="n">
         <v>44797</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+      <c r="E43" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
         <v>1.8</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K43" t="n">
         <v>8</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>4</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>8</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S43" t="n">
         <v>16</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T43" t="n">
         <v>24</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U43" t="n">
         <v>24</v>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>Dvärgfjällskivling
 Granrotspindling
@@ -6071,107 +6204,107 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="W42">
+      <c r="W43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 35141-2022 artfynd.xlsx", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="X42">
+      <c r="X43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 35141-2022 karta.png", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 35141-2022 georefererad karta.tif", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="AA42">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 35141-2022 FSC-klagomål.docx", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="AB42">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 35141-2022 FSC-klagomål mail.docx", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="AC42">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 35141-2022 tillsynsbegäran.docx", "A 35141-2022")</f>
         <v/>
       </c>
-      <c r="AD42">
+      <c r="AD43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 35141-2022 tillsynsbegäran mail.docx", "A 35141-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>A 2213-2023</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D44" s="1" t="n">
         <v>44942</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
+      <c r="E44" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
         <v>2.7</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>2</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L44" t="n">
         <v>10</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>4</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
         <v>14</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>4</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S44" t="n">
         <v>16</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T44" t="n">
         <v>35</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U44" t="n">
         <v>18</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Garderönn
 Granrotspindling
@@ -6191,107 +6324,107 @@
 Olivspindling</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 2213-2023 artfynd.xlsx", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 2213-2023 karta.png", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 2213-2023 georefererad karta.tif", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 2213-2023 FSC-klagomål.docx", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 2213-2023 FSC-klagomål mail.docx", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 2213-2023 tillsynsbegäran.docx", "A 2213-2023")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 2213-2023 tillsynsbegäran mail.docx", "A 2213-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>A 25779-2022</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D45" s="1" t="n">
         <v>44733</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
+      <c r="E45" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
         <v>12.6</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>4</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K45" t="n">
         <v>8</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L45" t="n">
         <v>5</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>2</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>8</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>3</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S45" t="n">
         <v>16</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T45" t="n">
         <v>30</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U45" t="n">
         <v>5</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Ruttaggsvamp
 Duvspindling
@@ -6311,111 +6444,111 @@
 Zontaggsvamp</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 25779-2022 artfynd.xlsx", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 25779-2022 karta.png", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 25779-2022 georefererad karta.tif", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="Z44">
+      <c r="Z45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/knärot/A 25779-2022 karta knärot.png", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 25779-2022 FSC-klagomål.docx", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 25779-2022 FSC-klagomål mail.docx", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 25779-2022 tillsynsbegäran.docx", "A 25779-2022")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 25779-2022 tillsynsbegäran mail.docx", "A 25779-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>A 9540-2026</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D46" s="1" t="n">
         <v>46071</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
+      <c r="E46" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>2.8</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>5</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L46" t="n">
         <v>5</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M46" t="n">
         <v>6</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>11</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>6</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S46" t="n">
         <v>16</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T46" t="n">
         <v>48</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>48</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Clitopaxillus alexandri
 Duvspindling
@@ -6435,107 +6568,107 @@
 Toppvaxing</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 9540-2026 artfynd.xlsx", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 9540-2026 karta.png", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 9540-2026 georefererad karta.tif", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 9540-2026 FSC-klagomål.docx", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 9540-2026 FSC-klagomål mail.docx", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 9540-2026 tillsynsbegäran.docx", "A 9540-2026")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 9540-2026 tillsynsbegäran mail.docx", "A 9540-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>A 44204-2022</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D47" s="1" t="n">
         <v>44839</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
+      <c r="E47" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GOTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>GOTLAND</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J47" t="n">
         <v>4</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K47" t="n">
         <v>3</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L47" t="n">
         <v>6</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>3</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>2</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>11</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>5</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S47" t="n">
         <v>16</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T47" t="n">
         <v>104</v>
       </c>
-      <c r="U46" t="n">
+      <c r="U47" t="n">
         <v>104</v>
       </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Bitter taggsvamp
 Sienamusseron
@@ -6555,160 +6688,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 44204-2022 artfynd.xlsx", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 44204-2022 karta.png", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 44204-2022 georefererad karta.tif", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 44204-2022 FSC-klagomål.docx", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 44204-2022 FSC-klagomål mail.docx", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 44204-2022 tillsynsbegäran.docx", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 44204-2022 tillsynsbegäran mail.docx", "A 44204-2022")</f>
         <v/>
       </c>
-      <c r="AE46">
+      <c r="AE47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 44204-2022 prioriterade fågelarter.docx", "A 44204-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 1477-2024</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45305</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>GOTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>GOTLAND</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3</v>
-      </c>
-      <c r="K47" t="n">
-        <v>4</v>
-      </c>
-      <c r="L47" t="n">
-        <v>5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>10</v>
-      </c>
-      <c r="R47" t="n">
-        <v>5</v>
-      </c>
-      <c r="S47" t="n">
-        <v>16</v>
-      </c>
-      <c r="T47" t="n">
-        <v>38</v>
-      </c>
-      <c r="U47" t="n">
-        <v>38</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Fågelträcksspindling
-Granrotspindling
-Igelkott
-Svartgrön spindling
-Vit taggsvamp
-Backtimjan
-Blå slemspindling
-Flattoppad klubbsvamp
-Odörspindling
-Sårläka
-Diskvaxskivling
-Nästrot
-Purpurknipprot
-Svavelriska
-Kransmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/artfynd/A 1477-2024 artfynd.xlsx", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor/A 1477-2024 karta.png", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/kartor_geotiff/A 1477-2024 georefererad karta.tif", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomål/A 1477-2024 FSC-klagomål.docx", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/klagomålsmail/A 1477-2024 FSC-klagomål mail.docx", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsyn/A 1477-2024 tillsynsbegäran.docx", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/tillsynsmail/A 1477-2024 tillsynsbegäran mail.docx", "A 1477-2024")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0980/fåglar/A 1477-2024 prioriterade fågelarter.docx", "A 1477-2024")</f>
         <v/>
       </c>
     </row>
@@ -6732,7 +6741,7 @@
         <v>45183</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6851,7 +6860,7 @@
         <v>44949</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6970,7 +6979,7 @@
         <v>46010</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7093,7 +7102,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7211,7 +7220,7 @@
         <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7329,7 +7338,7 @@
         <v>45518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7451,7 +7460,7 @@
         <v>45393</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7573,7 +7582,7 @@
         <v>46076</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7695,7 +7704,7 @@
         <v>44741</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7812,7 +7821,7 @@
         <v>45336</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7928,7 +7937,7 @@
         <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8048,7 +8057,7 @@
         <v>45418</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8164,7 +8173,7 @@
         <v>45179</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8280,7 +8289,7 @@
         <v>45526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8396,7 +8405,7 @@
         <v>44943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8511,7 +8520,7 @@
         <v>45774</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8626,7 +8635,7 @@
         <v>45096</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8745,7 +8754,7 @@
         <v>46044</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8860,7 +8869,7 @@
         <v>44517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8978,7 +8987,7 @@
         <v>44928</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9092,7 +9101,7 @@
         <v>45512</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9210,7 +9219,7 @@
         <v>45491</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9324,7 +9333,7 @@
         <v>45446</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9438,7 +9447,7 @@
         <v>45576</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9552,7 +9561,7 @@
         <v>45691</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9670,7 +9679,7 @@
         <v>46318</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9784,7 +9793,7 @@
         <v>45425</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9903,7 +9912,7 @@
         <v>44841</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10017,7 +10026,7 @@
         <v>45622</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10131,7 +10140,7 @@
         <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10248,7 +10257,7 @@
         <v>46010</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10365,7 +10374,7 @@
         <v>46119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10487,7 +10496,7 @@
         <v>44929</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10600,7 +10609,7 @@
         <v>44968</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10713,7 +10722,7 @@
         <v>45336</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10831,7 +10840,7 @@
         <v>45439</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10943,7 +10952,7 @@
         <v>45981</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11055,7 +11064,7 @@
         <v>46071</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11167,7 +11176,7 @@
         <v>46071</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11279,7 +11288,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11395,7 +11404,7 @@
         <v>44939</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11507,7 +11516,7 @@
         <v>46057</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11623,7 +11632,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11735,7 +11744,7 @@
         <v>45233</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11851,7 +11860,7 @@
         <v>44968</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11963,7 +11972,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12074,7 +12083,7 @@
         <v>45854</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12185,7 +12194,7 @@
         <v>44939</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12296,7 +12305,7 @@
         <v>44924</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12407,7 +12416,7 @@
         <v>46035</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12518,7 +12527,7 @@
         <v>45524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12629,7 +12638,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12740,7 +12749,7 @@
         <v>44857</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12854,7 +12863,7 @@
         <v>45939</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12968,7 +12977,7 @@
         <v>45213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13078,7 +13087,7 @@
         <v>45183</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13188,7 +13197,7 @@
         <v>45439</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13302,7 +13311,7 @@
         <v>44510</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13412,7 +13421,7 @@
         <v>46226</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13522,7 +13531,7 @@
         <v>46288</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13636,7 +13645,7 @@
         <v>45411</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13750,7 +13759,7 @@
         <v>45701</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13865,7 +13874,7 @@
         <v>45335</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13974,7 +13983,7 @@
         <v>44974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14083,7 +14092,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14192,7 +14201,7 @@
         <v>45980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14301,7 +14310,7 @@
         <v>44881</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14410,7 +14419,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14519,7 +14528,7 @@
         <v>45183</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14628,7 +14637,7 @@
         <v>45567</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14737,7 +14746,7 @@
         <v>45166</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14848,7 +14857,7 @@
         <v>44040</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14957,7 +14966,7 @@
         <v>45856</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15065,7 +15074,7 @@
         <v>45628</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15173,7 +15182,7 @@
         <v>45159</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15281,7 +15290,7 @@
         <v>45233</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15389,7 +15398,7 @@
         <v>46286</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15501,7 +15510,7 @@
         <v>46114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15609,7 +15618,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15717,7 +15726,7 @@
         <v>46062</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15825,7 +15834,7 @@
         <v>44915</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15933,7 +15942,7 @@
         <v>46055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16041,7 +16050,7 @@
         <v>45692</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16149,7 +16158,7 @@
         <v>45673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16257,7 +16266,7 @@
         <v>45264</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16365,7 +16374,7 @@
         <v>46185</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16472,7 +16481,7 @@
         <v>45366</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16583,7 +16592,7 @@
         <v>46129</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16694,7 +16703,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16801,7 +16810,7 @@
         <v>45695</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16908,7 +16917,7 @@
         <v>45673</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17015,7 +17024,7 @@
         <v>44833</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17122,7 +17131,7 @@
         <v>45524</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17229,7 +17238,7 @@
         <v>44508</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17341,7 +17350,7 @@
         <v>45531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17448,7 +17457,7 @@
         <v>45040</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17555,7 +17564,7 @@
         <v>45617</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17662,7 +17671,7 @@
         <v>44647</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17773,7 +17782,7 @@
         <v>45183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17880,7 +17889,7 @@
         <v>45378</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17987,7 +17996,7 @@
         <v>45205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18094,7 +18103,7 @@
         <v>45265</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18201,7 +18210,7 @@
         <v>44839</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18307,7 +18316,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18413,7 +18422,7 @@
         <v>44698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18519,7 +18528,7 @@
         <v>45665</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18625,7 +18634,7 @@
         <v>45840</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18735,7 +18744,7 @@
         <v>45595</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18841,7 +18850,7 @@
         <v>45236</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18947,7 +18956,7 @@
         <v>45477</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19053,7 +19062,7 @@
         <v>45467</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19159,7 +19168,7 @@
         <v>46190</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19269,7 +19278,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19380,7 +19389,7 @@
         <v>46084</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19486,7 +19495,7 @@
         <v>46009</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19597,7 +19606,7 @@
         <v>46008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19708,7 +19717,7 @@
         <v>46260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19818,7 +19827,7 @@
         <v>46008</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19929,7 +19938,7 @@
         <v>45301</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20035,7 +20044,7 @@
         <v>45097</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20141,7 +20150,7 @@
         <v>44609</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20251,7 +20260,7 @@
         <v>44603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20357,7 +20366,7 @@
         <v>45477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20463,7 +20472,7 @@
         <v>45198</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20569,7 +20578,7 @@
         <v>44628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20674,7 +20683,7 @@
         <v>44771</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20779,7 +20788,7 @@
         <v>44678</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20884,7 +20893,7 @@
         <v>45072</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20994,7 +21003,7 @@
         <v>45097</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21099,7 +21108,7 @@
         <v>45335</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21204,7 +21213,7 @@
         <v>45379</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21309,7 +21318,7 @@
         <v>45448</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21414,7 +21423,7 @@
         <v>44847</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21519,7 +21528,7 @@
         <v>44896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21624,7 +21633,7 @@
         <v>44725</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21729,7 +21738,7 @@
         <v>45212</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21834,7 +21843,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21939,7 +21948,7 @@
         <v>46125</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22044,7 +22053,7 @@
         <v>46148</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22149,7 +22158,7 @@
         <v>44511</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22259,7 +22268,7 @@
         <v>45700</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22368,7 +22377,7 @@
         <v>45720</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22473,7 +22482,7 @@
         <v>45524</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22578,7 +22587,7 @@
         <v>45363</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22683,7 +22692,7 @@
         <v>46048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22788,7 +22797,7 @@
         <v>46052</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22893,7 +22902,7 @@
         <v>45467</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22998,7 +23007,7 @@
         <v>45830</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23103,7 +23112,7 @@
         <v>46203</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23208,7 +23217,7 @@
         <v>45687</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23313,7 +23322,7 @@
         <v>44917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23418,7 +23427,7 @@
         <v>44755</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23523,7 +23532,7 @@
         <v>45403</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23628,7 +23637,7 @@
         <v>44968</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23733,7 +23742,7 @@
         <v>44508</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23843,7 +23852,7 @@
         <v>44986</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23948,7 +23957,7 @@
         <v>44839</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24053,7 +24062,7 @@
         <v>45212</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24158,7 +24167,7 @@
         <v>44530</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24263,7 +24272,7 @@
         <v>44934</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24368,7 +24377,7 @@
         <v>45595</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24473,7 +24482,7 @@
         <v>45582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24578,7 +24587,7 @@
         <v>44504</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24683,7 +24692,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24788,7 +24797,7 @@
         <v>45705</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24893,7 +24902,7 @@
         <v>45338</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24998,7 +25007,7 @@
         <v>44821</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25103,7 +25112,7 @@
         <v>45302</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25208,7 +25217,7 @@
         <v>45159</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25313,7 +25322,7 @@
         <v>44889</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25418,7 +25427,7 @@
         <v>44824</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25523,7 +25532,7 @@
         <v>45688</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25628,7 +25637,7 @@
         <v>46202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25733,7 +25742,7 @@
         <v>44839</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25806,7 +25815,7 @@
         <v>44674</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25879,7 +25888,7 @@
         <v>44725</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25952,7 +25961,7 @@
         <v>44713</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26025,7 +26034,7 @@
         <v>44725</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26098,7 +26107,7 @@
         <v>44496</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26171,7 +26180,7 @@
         <v>44538</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26244,7 +26253,7 @@
         <v>44713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26317,7 +26326,7 @@
         <v>44841</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26390,7 +26399,7 @@
         <v>44876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26468,7 +26477,7 @@
         <v>44515</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26541,7 +26550,7 @@
         <v>44652</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26614,7 +26623,7 @@
         <v>44647</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26687,7 +26696,7 @@
         <v>44647</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26760,7 +26769,7 @@
         <v>45281</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26833,7 +26842,7 @@
         <v>45282</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26906,7 +26915,7 @@
         <v>45733</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26979,7 +26988,7 @@
         <v>45852</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27052,7 +27061,7 @@
         <v>45852</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27125,7 +27134,7 @@
         <v>44760</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27198,7 +27207,7 @@
         <v>44699</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27276,7 +27285,7 @@
         <v>45891</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27349,7 +27358,7 @@
         <v>45895</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27422,7 +27431,7 @@
         <v>44955</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27500,7 +27509,7 @@
         <v>44955</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27573,7 +27582,7 @@
         <v>44818</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27646,7 +27655,7 @@
         <v>45607</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27719,7 +27728,7 @@
         <v>44931</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27792,7 +27801,7 @@
         <v>44963</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27865,7 +27874,7 @@
         <v>45764</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27938,7 +27947,7 @@
         <v>44944</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28011,7 +28020,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28084,7 +28093,7 @@
         <v>44988</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28162,7 +28171,7 @@
         <v>44944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28235,7 +28244,7 @@
         <v>45177</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28308,7 +28317,7 @@
         <v>45716</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28381,7 +28390,7 @@
         <v>45806</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28454,7 +28463,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28527,7 +28536,7 @@
         <v>45928</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28600,7 +28609,7 @@
         <v>45461</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28673,7 +28682,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28746,7 +28755,7 @@
         <v>46170</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28819,7 +28828,7 @@
         <v>45931</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28892,7 +28901,7 @@
         <v>44705</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28965,7 +28974,7 @@
         <v>44929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29038,7 +29047,7 @@
         <v>44944</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29111,7 +29120,7 @@
         <v>45327</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29184,7 +29193,7 @@
         <v>45222</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29257,7 +29266,7 @@
         <v>44882</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29330,7 +29339,7 @@
         <v>45931</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29403,7 +29412,7 @@
         <v>45939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29476,7 +29485,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29549,7 +29558,7 @@
         <v>44733</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29622,7 +29631,7 @@
         <v>45183</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29695,7 +29704,7 @@
         <v>44741</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29773,7 +29782,7 @@
         <v>45072</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29846,7 +29855,7 @@
         <v>45078</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29924,7 +29933,7 @@
         <v>45132</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29997,7 +30006,7 @@
         <v>45370</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30070,7 +30079,7 @@
         <v>45443</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30143,7 +30152,7 @@
         <v>45475</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30216,7 +30225,7 @@
         <v>44841</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30289,7 +30298,7 @@
         <v>45743</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30362,7 +30371,7 @@
         <v>45207</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30435,7 +30444,7 @@
         <v>44516</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30508,7 +30517,7 @@
         <v>45734</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30581,7 +30590,7 @@
         <v>44839</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30654,7 +30663,7 @@
         <v>45250</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30727,7 +30736,7 @@
         <v>46184</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30800,7 +30809,7 @@
         <v>45301</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30873,7 +30882,7 @@
         <v>45071</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30946,7 +30955,7 @@
         <v>45102</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31019,7 +31028,7 @@
         <v>45183</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31092,7 +31101,7 @@
         <v>45680</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31165,7 +31174,7 @@
         <v>45539</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31238,7 +31247,7 @@
         <v>45197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31311,7 +31320,7 @@
         <v>45978</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31384,7 +31393,7 @@
         <v>45363</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31457,7 +31466,7 @@
         <v>45314</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31530,7 +31539,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31603,7 +31612,7 @@
         <v>44819</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31681,7 +31690,7 @@
         <v>45499</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31754,7 +31763,7 @@
         <v>45418</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31827,7 +31836,7 @@
         <v>45013</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31900,7 +31909,7 @@
         <v>44896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31973,7 +31982,7 @@
         <v>45638</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32046,7 +32055,7 @@
         <v>45706</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32119,7 +32128,7 @@
         <v>45615</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32192,7 +32201,7 @@
         <v>45695</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32265,7 +32274,7 @@
         <v>46218</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32338,7 +32347,7 @@
         <v>45349</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32411,7 +32420,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32484,7 +32493,7 @@
         <v>46226</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32557,7 +32566,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32630,7 +32639,7 @@
         <v>46237</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32703,7 +32712,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32776,7 +32785,7 @@
         <v>46000</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32849,7 +32858,7 @@
         <v>45240</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32922,7 +32931,7 @@
         <v>45368</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32995,7 +33004,7 @@
         <v>46024</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33068,7 +33077,7 @@
         <v>45103</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33141,7 +33150,7 @@
         <v>45441</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33214,7 +33223,7 @@
         <v>46282</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33287,7 +33296,7 @@
         <v>46286</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33360,7 +33369,7 @@
         <v>46286</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33433,7 +33442,7 @@
         <v>46240</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33506,7 +33515,7 @@
         <v>45274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33579,7 +33588,7 @@
         <v>46036</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33652,7 +33661,7 @@
         <v>45791</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33725,7 +33734,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33798,7 +33807,7 @@
         <v>45793</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33871,7 +33880,7 @@
         <v>46154</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33944,7 +33953,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34017,7 +34026,7 @@
         <v>46163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34090,7 +34099,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34163,7 +34172,7 @@
         <v>46048</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34236,7 +34245,7 @@
         <v>46188</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34309,7 +34318,7 @@
         <v>46048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34382,7 +34391,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34455,7 +34464,7 @@
         <v>45693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34528,7 +34537,7 @@
         <v>46076</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34601,7 +34610,7 @@
         <v>46293</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34674,7 +34683,7 @@
         <v>46062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34747,7 +34756,7 @@
         <v>46292</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34820,7 +34829,7 @@
         <v>46036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34893,7 +34902,7 @@
         <v>45706</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34966,7 +34975,7 @@
         <v>45709</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35039,7 +35048,7 @@
         <v>45895</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35112,7 +35121,7 @@
         <v>46071</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35185,7 +35194,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35258,7 +35267,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35331,7 +35340,7 @@
         <v>45822</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35404,7 +35413,7 @@
         <v>45632</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35477,7 +35486,7 @@
         <v>46040</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35550,7 +35559,7 @@
         <v>46195</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35623,7 +35632,7 @@
         <v>46300</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35696,7 +35705,7 @@
         <v>45750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35769,7 +35778,7 @@
         <v>45491</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35842,7 +35851,7 @@
         <v>46298</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35915,7 +35924,7 @@
         <v>44938</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35988,7 +35997,7 @@
         <v>46280</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36061,7 +36070,7 @@
         <v>46198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36134,7 +36143,7 @@
         <v>46301</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36207,7 +36216,7 @@
         <v>45852</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36280,7 +36289,7 @@
         <v>45514</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36353,7 +36362,7 @@
         <v>45337</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36426,7 +36435,7 @@
         <v>46301</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36499,7 +36508,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36572,7 +36581,7 @@
         <v>45571</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36645,7 +36654,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36718,7 +36727,7 @@
         <v>45830</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36796,7 +36805,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36869,7 +36878,7 @@
         <v>45763</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36942,7 +36951,7 @@
         <v>45852</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37015,7 +37024,7 @@
         <v>45635</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37088,7 +37097,7 @@
         <v>45521</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37161,7 +37170,7 @@
         <v>45698</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37234,7 +37243,7 @@
         <v>45779</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37307,7 +37316,7 @@
         <v>45764</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37380,7 +37389,7 @@
         <v>46128</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37458,7 +37467,7 @@
         <v>45477</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37531,7 +37540,7 @@
         <v>45647</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37604,7 +37613,7 @@
         <v>45807</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37677,7 +37686,7 @@
         <v>45823</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37750,7 +37759,7 @@
         <v>45804</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37823,7 +37832,7 @@
         <v>45673</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37896,7 +37905,7 @@
         <v>46309</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37969,7 +37978,7 @@
         <v>45772</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38042,7 +38051,7 @@
         <v>45837</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38115,7 +38124,7 @@
         <v>45575</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38188,7 +38197,7 @@
         <v>45737</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38266,7 +38275,7 @@
         <v>46268</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38344,7 +38353,7 @@
         <v>46268</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38422,7 +38431,7 @@
         <v>46213</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38495,7 +38504,7 @@
         <v>46057</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38573,7 +38582,7 @@
         <v>45418</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38646,7 +38655,7 @@
         <v>45161</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38719,7 +38728,7 @@
         <v>46316</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38792,7 +38801,7 @@
         <v>45147</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38865,7 +38874,7 @@
         <v>45335</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38938,7 +38947,7 @@
         <v>46213</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39011,7 +39020,7 @@
         <v>44936</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39084,7 +39093,7 @@
         <v>45246</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39157,7 +39166,7 @@
         <v>46317</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39230,7 +39239,7 @@
         <v>45595</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39303,7 +39312,7 @@
         <v>44944</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39376,7 +39385,7 @@
         <v>45709</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39449,7 +39458,7 @@
         <v>45705</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39522,7 +39531,7 @@
         <v>45705</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39595,7 +39604,7 @@
         <v>44699</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39673,7 +39682,7 @@
         <v>44855</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39746,7 +39755,7 @@
         <v>44897</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39819,7 +39828,7 @@
         <v>46154</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39892,7 +39901,7 @@
         <v>45112</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39965,7 +39974,7 @@
         <v>46154</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40038,7 +40047,7 @@
         <v>46154</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40111,7 +40120,7 @@
         <v>44968</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40184,7 +40193,7 @@
         <v>45076</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40257,7 +40266,7 @@
         <v>45278</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40330,7 +40339,7 @@
         <v>45852</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40408,7 +40417,7 @@
         <v>45671</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40481,7 +40490,7 @@
         <v>45056</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40554,7 +40563,7 @@
         <v>45000</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40627,7 +40636,7 @@
         <v>45672</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40700,7 +40709,7 @@
         <v>44998</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40773,7 +40782,7 @@
         <v>44929</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40846,7 +40855,7 @@
         <v>44929</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40919,7 +40928,7 @@
         <v>45161</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40992,7 +41001,7 @@
         <v>45602</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41065,7 +41074,7 @@
         <v>45669</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41138,7 +41147,7 @@
         <v>45187</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41211,7 +41220,7 @@
         <v>45722</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41284,7 +41293,7 @@
         <v>45029</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41357,7 +41366,7 @@
         <v>45653</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41430,7 +41439,7 @@
         <v>44987</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41503,7 +41512,7 @@
         <v>44988</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41581,7 +41590,7 @@
         <v>45691</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41654,7 +41663,7 @@
         <v>44833</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41727,7 +41736,7 @@
         <v>45695</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41800,7 +41809,7 @@
         <v>45695</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41873,7 +41882,7 @@
         <v>45212</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41946,7 +41955,7 @@
         <v>45039</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42024,7 +42033,7 @@
         <v>45197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42097,7 +42106,7 @@
         <v>45418</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42170,7 +42179,7 @@
         <v>45705</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42243,7 +42252,7 @@
         <v>45601</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42316,7 +42325,7 @@
         <v>44936</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42389,7 +42398,7 @@
         <v>45670</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42462,7 +42471,7 @@
         <v>45086</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42535,7 +42544,7 @@
         <v>45079</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42608,7 +42617,7 @@
         <v>44959</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42681,7 +42690,7 @@
         <v>44968</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42754,7 +42763,7 @@
         <v>45058</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42827,7 +42836,7 @@
         <v>45301</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42900,7 +42909,7 @@
         <v>45203</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42973,7 +42982,7 @@
         <v>44909</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43046,7 +43055,7 @@
         <v>45103</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43119,7 +43128,7 @@
         <v>45190</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43192,7 +43201,7 @@
         <v>45322</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43265,7 +43274,7 @@
         <v>45575</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43338,7 +43347,7 @@
         <v>44959</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43411,7 +43420,7 @@
         <v>45576</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43484,7 +43493,7 @@
         <v>44974</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43557,7 +43566,7 @@
         <v>45284</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43630,7 +43639,7 @@
         <v>45593</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43703,7 +43712,7 @@
         <v>45415</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43776,7 +43785,7 @@
         <v>45401</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43849,7 +43858,7 @@
         <v>45336</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43922,7 +43931,7 @@
         <v>44881</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43995,7 +44004,7 @@
         <v>45407</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44068,7 +44077,7 @@
         <v>45173</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44141,7 +44150,7 @@
         <v>45394</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44214,7 +44223,7 @@
         <v>45509</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44287,7 +44296,7 @@
         <v>45733</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44360,7 +44369,7 @@
         <v>45585</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44433,7 +44442,7 @@
         <v>44624</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44506,7 +44515,7 @@
         <v>45667</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44579,7 +44588,7 @@
         <v>44818</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44652,7 +44661,7 @@
         <v>45597</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44725,7 +44734,7 @@
         <v>45197</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44798,7 +44807,7 @@
         <v>45440</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44871,7 +44880,7 @@
         <v>44609</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44944,7 +44953,7 @@
         <v>45072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45017,7 +45026,7 @@
         <v>45652</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45090,7 +45099,7 @@
         <v>44698</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45163,7 +45172,7 @@
         <v>45728</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45236,7 +45245,7 @@
         <v>45163</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45309,7 +45318,7 @@
         <v>45183</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45382,7 +45391,7 @@
         <v>45415</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45455,7 +45464,7 @@
         <v>45180</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45528,7 +45537,7 @@
         <v>45301</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45601,7 +45610,7 @@
         <v>45070</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45674,7 +45683,7 @@
         <v>45730</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45747,7 +45756,7 @@
         <v>45397</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45820,7 +45829,7 @@
         <v>45301</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45893,7 +45902,7 @@
         <v>45265</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45966,7 +45975,7 @@
         <v>44496</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46039,7 +46048,7 @@
         <v>45541</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46112,7 +46121,7 @@
         <v>44712</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46185,7 +46194,7 @@
         <v>44881</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46258,7 +46267,7 @@
         <v>45290</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46331,7 +46340,7 @@
         <v>44682</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46404,7 +46413,7 @@
         <v>44909</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46477,7 +46486,7 @@
         <v>45376</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46550,7 +46559,7 @@
         <v>45561</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46623,7 +46632,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46696,7 +46705,7 @@
         <v>45406</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46769,7 +46778,7 @@
         <v>45350</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46842,7 +46851,7 @@
         <v>45209</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46915,7 +46924,7 @@
         <v>44846</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46988,7 +46997,7 @@
         <v>45390</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47061,7 +47070,7 @@
         <v>45237</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47134,7 +47143,7 @@
         <v>45645</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47207,7 +47216,7 @@
         <v>45784</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47280,7 +47289,7 @@
         <v>45876</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47353,7 +47362,7 @@
         <v>46139</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47426,7 +47435,7 @@
         <v>45726</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47499,7 +47508,7 @@
         <v>46149</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
